--- a/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_bega_nowra_freemans.xlsx
+++ b/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_bega_nowra_freemans.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30331"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB5B2B62-79F5-4951-849D-DEE6310D7EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="548" documentId="11_30B5CDC3E51E25950AC1482F055FA59E38A43E3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30107364-363A-44A3-A060-5E061CB25656}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farm labels" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Farm labels'!$A$1:$AB$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Image labels'!$A$1:$G$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Image labels'!$F$1:$F$267</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="413">
   <si>
     <t>source</t>
   </si>
@@ -813,6 +813,9 @@
     <t>70550/buildings/FreemansReach__FreemanReachIMG.tif_farm_70550_building_6.tif</t>
   </si>
   <si>
+    <t>Horse/Poultry</t>
+  </si>
+  <si>
     <t>70550/buildings/FreemansReach__FreemanReachIMG.tif_farm_70550_building_7.tif</t>
   </si>
   <si>
@@ -964,6 +967,9 @@
   </si>
   <si>
     <t>70625/buildings/FreemansReach__FreemanReachIMG.tif_farm_70625_building_1.tif</t>
+  </si>
+  <si>
+    <t>Poultry/Freerange pigs</t>
   </si>
   <si>
     <t>70625/buildings/FreemansReach__FreemanReachIMG.tif_farm_70625_building_2.tif</t>
@@ -3105,8 +3111,12 @@
       <c r="S29" s="9"/>
       <c r="T29" s="10"/>
       <c r="U29" s="9"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="9"/>
+      <c r="V29" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="W29" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="X29" s="10" t="s">
         <v>30</v>
       </c>
@@ -5875,8 +5885,12 @@
       <c r="G95" s="5"/>
       <c r="H95" s="6"/>
       <c r="I95" s="5"/>
-      <c r="J95" s="6"/>
-      <c r="K95" s="5"/>
+      <c r="J95" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="L95" s="6" t="s">
         <v>30</v>
       </c>
@@ -5935,8 +5949,12 @@
       <c r="S96" s="13"/>
       <c r="T96" s="14"/>
       <c r="U96" s="13"/>
-      <c r="V96" s="14"/>
-      <c r="W96" s="13"/>
+      <c r="V96" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="W96" s="13" t="s">
+        <v>31</v>
+      </c>
       <c r="X96" s="14" t="s">
         <v>30</v>
       </c>
@@ -5948,7 +5966,6 @@
       <c r="AB96" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB96" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6116,7 +6133,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="46.5703125" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="77.28515625" customWidth="1"/>
@@ -8518,7 +8535,9 @@
       <c r="F114" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G114" s="11"/>
+      <c r="G114" s="11" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="8" t="s">
@@ -8534,7 +8553,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>141</v>
@@ -8555,7 +8574,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F116" s="10" t="s">
         <v>23</v>
@@ -8576,7 +8595,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F117" s="14" t="s">
         <v>23</v>
@@ -8597,7 +8616,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>141</v>
@@ -8618,7 +8637,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>141</v>
@@ -8639,7 +8658,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>23</v>
@@ -8660,7 +8679,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>141</v>
@@ -8681,7 +8700,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>23</v>
@@ -8702,7 +8721,7 @@
         <v>23</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>141</v>
@@ -8723,7 +8742,7 @@
         <v>144</v>
       </c>
       <c r="E124" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F124" s="10" t="s">
         <v>55</v>
@@ -8744,7 +8763,7 @@
         <v>144</v>
       </c>
       <c r="E125" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F125" s="14" t="s">
         <v>55</v>
@@ -8765,7 +8784,7 @@
         <v>144</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>11</v>
@@ -8786,7 +8805,7 @@
         <v>144</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>141</v>
@@ -8807,7 +8826,7 @@
         <v>144</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>141</v>
@@ -8828,7 +8847,7 @@
         <v>144</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>11</v>
@@ -8849,7 +8868,7 @@
         <v>144</v>
       </c>
       <c r="E130" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F130" s="14" t="s">
         <v>25</v>
@@ -8870,7 +8889,7 @@
         <v>144</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F131" s="17" t="s">
         <v>25</v>
@@ -8891,7 +8910,7 @@
         <v>23</v>
       </c>
       <c r="E132" s="12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F132" s="14" t="s">
         <v>25</v>
@@ -8912,7 +8931,7 @@
         <v>144</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>25</v>
@@ -8933,7 +8952,7 @@
         <v>144</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F134" s="14" t="s">
         <v>25</v>
@@ -8954,7 +8973,7 @@
         <v>144</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>25</v>
@@ -8975,7 +8994,7 @@
         <v>144</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>141</v>
@@ -8996,7 +9015,7 @@
         <v>144</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>141</v>
@@ -9017,7 +9036,7 @@
         <v>144</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F138" s="17" t="s">
         <v>141</v>
@@ -9038,7 +9057,7 @@
         <v>144</v>
       </c>
       <c r="E139" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F139" s="14" t="s">
         <v>15</v>
@@ -9059,7 +9078,7 @@
         <v>144</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>21</v>
@@ -9080,7 +9099,7 @@
         <v>144</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>141</v>
@@ -9101,7 +9120,7 @@
         <v>144</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>21</v>
@@ -9122,7 +9141,7 @@
         <v>144</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>141</v>
@@ -9143,7 +9162,7 @@
         <v>144</v>
       </c>
       <c r="E144" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F144" s="17" t="s">
         <v>141</v>
@@ -9164,7 +9183,7 @@
         <v>144</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>25</v>
@@ -9185,7 +9204,7 @@
         <v>144</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F146" s="10" t="s">
         <v>141</v>
@@ -9206,7 +9225,7 @@
         <v>144</v>
       </c>
       <c r="E147" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>141</v>
@@ -9227,7 +9246,7 @@
         <v>144</v>
       </c>
       <c r="E148" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F148" s="10" t="s">
         <v>141</v>
@@ -9248,7 +9267,7 @@
         <v>144</v>
       </c>
       <c r="E149" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F149" s="14" t="s">
         <v>141</v>
@@ -9269,7 +9288,7 @@
         <v>144</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>9</v>
@@ -9290,7 +9309,7 @@
         <v>144</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>9</v>
@@ -9311,7 +9330,7 @@
         <v>144</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>9</v>
@@ -9332,7 +9351,7 @@
         <v>144</v>
       </c>
       <c r="E153" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F153" s="17" t="s">
         <v>9</v>
@@ -9353,7 +9372,7 @@
         <v>144</v>
       </c>
       <c r="E154" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F154" s="10" t="s">
         <v>55</v>
@@ -9374,7 +9393,7 @@
         <v>144</v>
       </c>
       <c r="E155" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F155" s="14" t="s">
         <v>25</v>
@@ -9395,7 +9414,7 @@
         <v>23</v>
       </c>
       <c r="E156" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F156" s="17" t="s">
         <v>55</v>
@@ -9416,7 +9435,7 @@
         <v>144</v>
       </c>
       <c r="E157" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>55</v>
@@ -9437,7 +9456,7 @@
         <v>144</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F158" s="14" t="s">
         <v>25</v>
@@ -9458,7 +9477,7 @@
         <v>144</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>25</v>
@@ -9479,7 +9498,7 @@
         <v>144</v>
       </c>
       <c r="E160" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F160" s="17" t="s">
         <v>141</v>
@@ -9500,7 +9519,7 @@
         <v>144</v>
       </c>
       <c r="E161" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F161" s="14" t="s">
         <v>25</v>
@@ -9521,7 +9540,7 @@
         <v>144</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F162" s="17" t="s">
         <v>25</v>
@@ -9542,7 +9561,7 @@
         <v>23</v>
       </c>
       <c r="E163" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F163" s="14" t="s">
         <v>17</v>
@@ -9563,7 +9582,7 @@
         <v>23</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>9</v>
@@ -9584,12 +9603,14 @@
         <v>23</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G165" s="7"/>
+      <c r="G165" s="7" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="4" t="s">
@@ -9605,7 +9626,7 @@
         <v>23</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>23</v>
@@ -9626,12 +9647,14 @@
         <v>23</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G167" s="7"/>
+      <c r="G167" s="7" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="4" t="s">
@@ -9647,7 +9670,7 @@
         <v>23</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>9</v>
@@ -9668,12 +9691,14 @@
         <v>23</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G169" s="7"/>
+      <c r="G169" s="7" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="4" t="s">
@@ -9689,7 +9714,7 @@
         <v>23</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>23</v>
@@ -9710,7 +9735,7 @@
         <v>23</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>9</v>
@@ -9731,7 +9756,7 @@
         <v>23</v>
       </c>
       <c r="E172" s="16" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F172" s="17" t="s">
         <v>23</v>
@@ -9752,7 +9777,7 @@
         <v>144</v>
       </c>
       <c r="E173" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F173" s="14" t="s">
         <v>25</v>
@@ -9773,7 +9798,7 @@
         <v>144</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>25</v>
@@ -9794,7 +9819,7 @@
         <v>144</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F175" s="17" t="s">
         <v>25</v>
@@ -9815,7 +9840,7 @@
         <v>144</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F176" s="14" t="s">
         <v>55</v>
@@ -9836,7 +9861,7 @@
         <v>144</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>141</v>
@@ -9857,7 +9882,7 @@
         <v>144</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>21</v>
@@ -9878,7 +9903,7 @@
         <v>144</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F179" s="17" t="s">
         <v>25</v>
@@ -9899,7 +9924,7 @@
         <v>17</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F180" s="10" t="s">
         <v>15</v>
@@ -9920,7 +9945,7 @@
         <v>17</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F181" s="10" t="s">
         <v>141</v>
@@ -9941,7 +9966,7 @@
         <v>17</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F182" s="10" t="s">
         <v>141</v>
@@ -9962,7 +9987,7 @@
         <v>17</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>15</v>
@@ -9983,7 +10008,7 @@
         <v>17</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F184" s="10" t="s">
         <v>141</v>
@@ -10004,7 +10029,7 @@
         <v>17</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F185" s="10" t="s">
         <v>141</v>
@@ -10025,7 +10050,7 @@
         <v>17</v>
       </c>
       <c r="E186" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F186" s="10" t="s">
         <v>141</v>
@@ -10046,7 +10071,7 @@
         <v>17</v>
       </c>
       <c r="E187" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F187" s="14" t="s">
         <v>25</v>
@@ -10067,7 +10092,7 @@
         <v>144</v>
       </c>
       <c r="E188" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F188" s="17" t="s">
         <v>96</v>
@@ -10088,7 +10113,7 @@
         <v>144</v>
       </c>
       <c r="E189" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F189" s="10" t="s">
         <v>141</v>
@@ -10109,7 +10134,7 @@
         <v>144</v>
       </c>
       <c r="E190" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F190" s="14" t="s">
         <v>25</v>
@@ -10130,7 +10155,7 @@
         <v>144</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F191" s="17" t="s">
         <v>25</v>
@@ -10151,7 +10176,7 @@
         <v>144</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F192" s="10" t="s">
         <v>141</v>
@@ -10172,7 +10197,7 @@
         <v>144</v>
       </c>
       <c r="E193" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>11</v>
@@ -10193,7 +10218,7 @@
         <v>144</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F194" s="10" t="s">
         <v>141</v>
@@ -10214,7 +10239,7 @@
         <v>144</v>
       </c>
       <c r="E195" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F195" s="14" t="s">
         <v>141</v>
@@ -10235,7 +10260,7 @@
         <v>144</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>55</v>
@@ -10256,7 +10281,7 @@
         <v>144</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F197" s="6" t="s">
         <v>141</v>
@@ -10277,7 +10302,7 @@
         <v>144</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>141</v>
@@ -10298,7 +10323,7 @@
         <v>144</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>141</v>
@@ -10319,7 +10344,7 @@
         <v>144</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F200" s="17" t="s">
         <v>96</v>
@@ -10340,7 +10365,7 @@
         <v>144</v>
       </c>
       <c r="E201" s="8" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F201" s="10" t="s">
         <v>25</v>
@@ -10361,7 +10386,7 @@
         <v>144</v>
       </c>
       <c r="E202" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F202" s="14" t="s">
         <v>11</v>
@@ -10382,7 +10407,7 @@
         <v>144</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>141</v>
@@ -10403,7 +10428,7 @@
         <v>144</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F204" s="17" t="s">
         <v>21</v>
@@ -10424,7 +10449,7 @@
         <v>144</v>
       </c>
       <c r="E205" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F205" s="14" t="s">
         <v>11</v>
@@ -10445,7 +10470,7 @@
         <v>144</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>25</v>
@@ -10466,7 +10491,7 @@
         <v>144</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>11</v>
@@ -10487,7 +10512,7 @@
         <v>144</v>
       </c>
       <c r="E208" s="16" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F208" s="17" t="s">
         <v>11</v>
@@ -10508,7 +10533,7 @@
         <v>144</v>
       </c>
       <c r="E209" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F209" s="14" t="s">
         <v>141</v>
@@ -10529,7 +10554,7 @@
         <v>144</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F210" s="17" t="s">
         <v>25</v>
@@ -10550,7 +10575,7 @@
         <v>144</v>
       </c>
       <c r="E211" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F211" s="14" t="s">
         <v>96</v>
@@ -10571,7 +10596,7 @@
         <v>144</v>
       </c>
       <c r="E212" s="16" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F212" s="17" t="s">
         <v>25</v>
@@ -10592,7 +10617,7 @@
         <v>144</v>
       </c>
       <c r="E213" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F213" s="14" t="s">
         <v>25</v>
@@ -10613,7 +10638,7 @@
         <v>144</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F214" s="6" t="s">
         <v>25</v>
@@ -10634,7 +10659,7 @@
         <v>144</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F215" s="17" t="s">
         <v>25</v>
@@ -10655,7 +10680,7 @@
         <v>144</v>
       </c>
       <c r="E216" s="12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F216" s="14" t="s">
         <v>96</v>
@@ -10676,7 +10701,7 @@
         <v>144</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F217" s="17" t="s">
         <v>55</v>
@@ -10697,7 +10722,7 @@
         <v>144</v>
       </c>
       <c r="E218" s="8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F218" s="10" t="s">
         <v>17</v>
@@ -10718,7 +10743,7 @@
         <v>144</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>141</v>
@@ -10739,7 +10764,7 @@
         <v>144</v>
       </c>
       <c r="E220" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F220" s="10" t="s">
         <v>141</v>
@@ -10760,7 +10785,7 @@
         <v>144</v>
       </c>
       <c r="E221" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F221" s="10" t="s">
         <v>17</v>
@@ -10781,7 +10806,7 @@
         <v>144</v>
       </c>
       <c r="E222" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F222" s="14" t="s">
         <v>141</v>
@@ -10802,7 +10827,7 @@
         <v>144</v>
       </c>
       <c r="E223" s="16" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>21</v>
@@ -10823,7 +10848,7 @@
         <v>144</v>
       </c>
       <c r="E224" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F224" s="10" t="s">
         <v>17</v>
@@ -10844,7 +10869,7 @@
         <v>144</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F225" s="14" t="s">
         <v>25</v>
@@ -10865,7 +10890,7 @@
         <v>144</v>
       </c>
       <c r="E226" s="16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F226" s="17" t="s">
         <v>17</v>
@@ -10886,7 +10911,7 @@
         <v>144</v>
       </c>
       <c r="E227" s="12" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F227" s="14" t="s">
         <v>25</v>
@@ -10907,7 +10932,7 @@
         <v>144</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>141</v>
@@ -10928,7 +10953,7 @@
         <v>144</v>
       </c>
       <c r="E229" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F229" s="17" t="s">
         <v>25</v>
@@ -10949,7 +10974,7 @@
         <v>144</v>
       </c>
       <c r="E230" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F230" s="14" t="s">
         <v>96</v>
@@ -10970,7 +10995,7 @@
         <v>144</v>
       </c>
       <c r="E231" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F231" s="17" t="s">
         <v>25</v>
@@ -10991,7 +11016,7 @@
         <v>144</v>
       </c>
       <c r="E232" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F232" s="14" t="s">
         <v>25</v>
@@ -11012,7 +11037,7 @@
         <v>144</v>
       </c>
       <c r="E233" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F233" s="17" t="s">
         <v>25</v>
@@ -11033,7 +11058,7 @@
         <v>144</v>
       </c>
       <c r="E234" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F234" s="14" t="s">
         <v>96</v>
@@ -11054,7 +11079,7 @@
         <v>144</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F235" s="6" t="s">
         <v>141</v>
@@ -11075,7 +11100,7 @@
         <v>144</v>
       </c>
       <c r="E236" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F236" s="17" t="s">
         <v>25</v>
@@ -11096,7 +11121,7 @@
         <v>144</v>
       </c>
       <c r="E237" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F237" s="14" t="s">
         <v>25</v>
@@ -11117,7 +11142,7 @@
         <v>144</v>
       </c>
       <c r="E238" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F238" s="17" t="s">
         <v>25</v>
@@ -11138,7 +11163,7 @@
         <v>144</v>
       </c>
       <c r="E239" s="12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F239" s="14" t="s">
         <v>96</v>
@@ -11159,7 +11184,7 @@
         <v>144</v>
       </c>
       <c r="E240" s="16" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F240" s="17" t="s">
         <v>25</v>
@@ -11180,7 +11205,7 @@
         <v>144</v>
       </c>
       <c r="E241" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F241" s="14" t="s">
         <v>25</v>
@@ -11201,7 +11226,7 @@
         <v>144</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>141</v>
@@ -11222,7 +11247,7 @@
         <v>144</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F243" s="6" t="s">
         <v>141</v>
@@ -11243,7 +11268,7 @@
         <v>144</v>
       </c>
       <c r="E244" s="16" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F244" s="17" t="s">
         <v>11</v>
@@ -11264,7 +11289,7 @@
         <v>144</v>
       </c>
       <c r="E245" s="12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F245" s="14" t="s">
         <v>25</v>
@@ -11285,7 +11310,7 @@
         <v>144</v>
       </c>
       <c r="E246" s="16" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F246" s="17" t="s">
         <v>141</v>
@@ -11306,7 +11331,7 @@
         <v>23</v>
       </c>
       <c r="E247" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>11</v>
@@ -11327,7 +11352,7 @@
         <v>23</v>
       </c>
       <c r="E248" s="8" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>141</v>
@@ -11348,7 +11373,7 @@
         <v>23</v>
       </c>
       <c r="E249" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>141</v>
@@ -11369,7 +11394,7 @@
         <v>23</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F250" s="10" t="s">
         <v>23</v>
@@ -11390,7 +11415,7 @@
         <v>23</v>
       </c>
       <c r="E251" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F251" s="10" t="s">
         <v>141</v>
@@ -11411,7 +11436,7 @@
         <v>23</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>141</v>
@@ -11432,7 +11457,7 @@
         <v>23</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F253" s="10" t="s">
         <v>141</v>
@@ -11453,7 +11478,7 @@
         <v>23</v>
       </c>
       <c r="E254" s="12" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F254" s="14" t="s">
         <v>23</v>
@@ -11474,7 +11499,7 @@
         <v>23</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F255" s="6" t="s">
         <v>23</v>
@@ -11495,7 +11520,7 @@
         <v>23</v>
       </c>
       <c r="E256" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>23</v>
@@ -11516,7 +11541,7 @@
         <v>23</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F257" s="6" t="s">
         <v>23</v>
@@ -11537,12 +11562,14 @@
         <v>23</v>
       </c>
       <c r="E258" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G258" s="7"/>
+      <c r="G258" s="7" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="4" t="s">
@@ -11558,7 +11585,7 @@
         <v>23</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F259" s="6" t="s">
         <v>23</v>
@@ -11579,7 +11606,7 @@
         <v>23</v>
       </c>
       <c r="E260" s="16" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F260" s="17" t="s">
         <v>11</v>
@@ -11600,7 +11627,7 @@
         <v>23</v>
       </c>
       <c r="E261" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F261" s="10" t="s">
         <v>23</v>
@@ -11621,7 +11648,7 @@
         <v>23</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F262" s="10" t="s">
         <v>141</v>
@@ -11642,7 +11669,7 @@
         <v>23</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F263" s="10" t="s">
         <v>23</v>
@@ -11663,12 +11690,14 @@
         <v>23</v>
       </c>
       <c r="E264" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F264" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="G264" s="11"/>
+      <c r="G264" s="11" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="8" t="s">
@@ -11684,7 +11713,7 @@
         <v>23</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F265" s="10" t="s">
         <v>55</v>
@@ -11705,7 +11734,7 @@
         <v>23</v>
       </c>
       <c r="E266" s="8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F266" s="10" t="s">
         <v>23</v>
@@ -11726,7 +11755,7 @@
         <v>23</v>
       </c>
       <c r="E267" s="12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F267" s="14" t="s">
         <v>23</v>
@@ -11734,7 +11763,6 @@
       <c r="G267" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G267" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -11752,15 +11780,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C2D78CD4D7E5E443850520BD8D915EF0" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75ad294e393f4787ac547a5ae7fd66fe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="94707517-fcf5-48ba-971e-d38caecd4d61" xmlns:ns3="73cbf0c7-d69e-427c-8bf4-4bd79e720451" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="396587b85e5f7bdb019044cddbd799be" ns2:_="" ns3:_="">
     <xsd:import namespace="94707517-fcf5-48ba-971e-d38caecd4d61"/>
@@ -11961,6 +11980,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11973,11 +12001,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D300C1-7FAB-47FA-B64E-CF3AD58F36BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E824D9A-1290-40EE-B13F-DC6C22188E15}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E824D9A-1290-40EE-B13F-DC6C22188E15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00D300C1-7FAB-47FA-B64E-CF3AD58F36BC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_bega_nowra_freemans.xlsx
+++ b/labelled_sheets/2026_07_24_generalisation_relabel_farm_and_image_bega_nowra_freemans.xlsx
@@ -622,12 +622,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Farm UID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -769,12 +769,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>farm-4c2a7788cb9d8c1b</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -832,12 +832,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
           <t>farm-51e241b57b38135a</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -887,12 +887,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>farm-8161fdb4fade82e4</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -946,12 +946,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
           <t>farm-0051b919c7e75dac</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1001,12 +1001,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
           <t>farm-85f4bdd4e03c2824</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
@@ -1056,12 +1056,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -1119,12 +1119,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
           <t>farm-ca85229a21a4f13a</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -1174,12 +1174,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
           <t>farm-107a0c871a7523dc</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -1229,12 +1229,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>farm-71b95be6dca0475d</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -1284,12 +1284,12 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -1343,12 +1343,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>farm-a8f955c75c7e0d0c</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
           <t>farm-d3ac9513e941235c</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -1461,12 +1461,12 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1516,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>farm-9005420ffa675cc2</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1571,12 +1571,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -1634,12 +1634,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
           <t>farm-e56757363b191415</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -1701,12 +1701,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>farm-7f29a9b7e4429b3f</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
@@ -1756,12 +1756,12 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>farm-eed961522354b1db</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -1823,12 +1823,12 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>farm-305accaece5919b4</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -1874,12 +1874,12 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
@@ -1937,12 +1937,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>farm-ac5c64319b646dd9</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -1988,12 +1988,12 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
           <t>farm-af5a261842357d7e</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
@@ -2043,12 +2043,12 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>farm-037e909e1f5ae0ac</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
@@ -2098,12 +2098,12 @@
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
           <t>farm-d4377432e11c0aae</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
@@ -2149,12 +2149,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>farm-bc1775332e31d3a0</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -2200,12 +2200,12 @@
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>farm-6027017933654175</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
@@ -2259,12 +2259,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -2334,12 +2334,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -2401,12 +2401,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
@@ -2460,12 +2460,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>farm-4fabfad6e9be445d</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -2511,12 +2511,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>farm-6663f1572ff9407d</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -2566,12 +2566,12 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>farm-b1275447db90b1b0</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -2621,12 +2621,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>farm-16a4bd6e448afbf7</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
@@ -2676,12 +2676,12 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>farm-db7d890c72e8d289</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
@@ -2735,12 +2735,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>farm-244ec28e52f7d3b6</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -2790,12 +2790,12 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>farm-48b1a81463554162</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -2845,12 +2845,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>farm-4e5cfd71f42aff27</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -2900,12 +2900,12 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
           <t>farm-76571ee6ee6ffd61</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
@@ -2955,12 +2955,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>farm-98dc08a8f634b5d1</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -3010,12 +3010,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>farm-403ed60a7fd41ebf</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -3069,12 +3069,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>farm-77ffc5161ce89cd6</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
@@ -3155,12 +3155,12 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
           <t>farm-9d61e7916f947b83</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
@@ -3214,12 +3214,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>farm-378faa814fbaed38</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -3269,12 +3269,12 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
           <t>farm-f31a7e9254df2121</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
@@ -3328,12 +3328,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
           <t>farm-0917e33745fd6d25</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -3383,12 +3383,12 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
           <t>farm-42126df81f405428</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
@@ -3438,12 +3438,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>farm-e1edc0ed277da384</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -3493,12 +3493,12 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
           <t>farm-6aee8825c7e649be</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
@@ -3552,12 +3552,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
@@ -3623,12 +3623,12 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
           <t>farm-b94a7f5d05ced20a</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
@@ -3678,12 +3678,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>farm-0eab511b21302fc0</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
@@ -3733,12 +3733,12 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
           <t>farm-5edef7fd5cc44bcc</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C54" s="8" t="n">
@@ -3784,12 +3784,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>farm-e04cb65e43342bea</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -3847,12 +3847,12 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
@@ -3914,12 +3914,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
           <t>farm-46c1097774477779</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
@@ -3965,12 +3965,12 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
           <t>farm-ca77d119c32310fd</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -4020,12 +4020,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>farm-de50bdf28a62bc88</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
@@ -4075,12 +4075,12 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
           <t>farm-50a7d5199634a0da</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -4130,12 +4130,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>farm-3b73264647357ca2</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
@@ -4181,12 +4181,12 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
           <t>farm-be47380be0097c75</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
@@ -4244,12 +4244,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>farm-f34e8576ace1680e</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
@@ -4299,12 +4299,12 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
           <t>farm-f646aac5897fa0a0</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -4354,12 +4354,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>farm-89a91fedcf7b3e2d</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
@@ -4409,12 +4409,12 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
           <t>farm-c8b49065835d2604</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -4460,12 +4460,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>farm-fbf74ce631c7a094</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
@@ -4515,12 +4515,12 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
           <t>farm-e206fc0bc6df3cad</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
@@ -4566,12 +4566,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
           <t>farm-9ca14a5bc58e10f9</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -4621,12 +4621,12 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
           <t>farm-d28006827dd1894b</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -4676,12 +4676,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
           <t>farm-b352036320a4167f</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
@@ -4731,12 +4731,12 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
           <t>farm-818947903f93d1f6</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -4782,12 +4782,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>farm-0a81d2f16e4f8496</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
@@ -4833,12 +4833,12 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
           <t>farm-393753335beb054e</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -4888,12 +4888,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
           <t>farm-b2341f5ff3f48af2</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
@@ -4943,12 +4943,12 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
           <t>farm-c5b8bbd58c7a19c7</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
@@ -5006,12 +5006,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
           <t>farm-9b31a7c4658ffbc4</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -5061,12 +5061,12 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
           <t>farm-b408aa99dd6b49c3</t>
-        </is>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
@@ -5116,12 +5116,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
           <t>farm-0d9cf959fea36fb6</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -5171,12 +5171,12 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
           <t>farm-dbffb518572c2a8e</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
@@ -5222,12 +5222,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
           <t>farm-8b490b53d3476ae3</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
@@ -5277,12 +5277,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
           <t>farm-79ebf6bb7857b01d</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -5332,12 +5332,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
           <t>farm-c4f666615a54cd69</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
@@ -5387,12 +5387,12 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>farm-2023e6494cc05395</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -5438,12 +5438,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
           <t>farm-2296fd66f82b7c0c</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
@@ -5493,12 +5493,12 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
           <t>farm-e74a59dfdf2ba825</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
@@ -5548,12 +5548,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
           <t>farm-ef359e9395f5316b</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C87" s="4" t="n">
@@ -5603,12 +5603,12 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
           <t>farm-cccfb0ef4c418994</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -5654,12 +5654,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
           <t>farm-c2e233ed7bdd157a</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
@@ -5709,12 +5709,12 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
           <t>farm-78156461891034d4</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
@@ -5764,12 +5764,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
           <t>farm-7a779bf2435f46d6</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -5819,12 +5819,12 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
           <t>farm-e449759ff2c26029</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
@@ -5874,12 +5874,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
           <t>farm-87ce4b159638edc3</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
@@ -5925,12 +5925,12 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -5992,12 +5992,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
@@ -6067,12 +6067,12 @@
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C96" s="12" t="n">
@@ -6345,12 +6345,12 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Farm UID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
           <t>farm-4c2a7788cb9d8c1b</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -6423,12 +6423,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
           <t>farm-4c2a7788cb9d8c1b</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
@@ -6459,12 +6459,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
           <t>farm-4c2a7788cb9d8c1b</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -6495,12 +6495,12 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
           <t>farm-4c2a7788cb9d8c1b</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C5" s="16" t="n">
@@ -6531,12 +6531,12 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
           <t>farm-51e241b57b38135a</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -6567,12 +6567,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
           <t>farm-51e241b57b38135a</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
@@ -6603,12 +6603,12 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
           <t>farm-51e241b57b38135a</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -6639,12 +6639,12 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
           <t>farm-51e241b57b38135a</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
@@ -6675,12 +6675,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>farm-8161fdb4fade82e4</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
@@ -6711,12 +6711,12 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
           <t>farm-8161fdb4fade82e4</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
@@ -6747,12 +6747,12 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
           <t>farm-0051b919c7e75dac</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -6783,12 +6783,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>farm-85f4bdd4e03c2824</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -6819,12 +6819,12 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
           <t>farm-85f4bdd4e03c2824</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
@@ -6855,12 +6855,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -6891,12 +6891,12 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -6927,12 +6927,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -6963,12 +6963,12 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -6999,12 +6999,12 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
@@ -7035,12 +7035,12 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
           <t>farm-457a8ccf0f2c1d66</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
@@ -7071,12 +7071,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>farm-ca85229a21a4f13a</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
@@ -7107,12 +7107,12 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>farm-ca85229a21a4f13a</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
@@ -7143,12 +7143,12 @@
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
           <t>farm-ca85229a21a4f13a</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -7179,12 +7179,12 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
           <t>farm-107a0c871a7523dc</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
@@ -7215,12 +7215,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>farm-71b95be6dca0475d</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -7251,12 +7251,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
           <t>farm-71b95be6dca0475d</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
@@ -7287,12 +7287,12 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
           <t>farm-71b95be6dca0475d</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -7323,12 +7323,12 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
@@ -7359,12 +7359,12 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
@@ -7395,12 +7395,12 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
@@ -7431,12 +7431,12 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
@@ -7467,12 +7467,12 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
@@ -7503,12 +7503,12 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
@@ -7539,12 +7539,12 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
@@ -7575,12 +7575,12 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
           <t>farm-66078959d9952157</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
@@ -7611,12 +7611,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>farm-a8f955c75c7e0d0c</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
@@ -7647,12 +7647,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>farm-a8f955c75c7e0d0c</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -7683,12 +7683,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
           <t>farm-a8f955c75c7e0d0c</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
@@ -7719,12 +7719,12 @@
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
           <t>farm-a8f955c75c7e0d0c</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
@@ -7755,12 +7755,12 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
           <t>farm-d3ac9513e941235c</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
@@ -7791,12 +7791,12 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>farm-d3ac9513e941235c</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
@@ -7827,12 +7827,12 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
           <t>farm-d3ac9513e941235c</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
@@ -7863,12 +7863,12 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
           <t>farm-d3ac9513e941235c</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
@@ -7899,12 +7899,12 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
           <t>farm-d3ac9513e941235c</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
@@ -7935,12 +7935,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -7971,12 +7971,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
@@ -8007,12 +8007,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
@@ -8043,12 +8043,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
@@ -8079,12 +8079,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
@@ -8115,12 +8115,12 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
           <t>farm-38adbff0f95f5b5b</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C50" s="16" t="n">
@@ -8151,12 +8151,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
           <t>farm-9005420ffa675cc2</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
@@ -8187,12 +8187,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
@@ -8223,12 +8223,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
@@ -8259,12 +8259,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
@@ -8295,12 +8295,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
@@ -8331,12 +8331,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
@@ -8367,12 +8367,12 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
           <t>farm-173d9788e4d124bb</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
@@ -8403,12 +8403,12 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
           <t>farm-e56757363b191415</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
@@ -8439,12 +8439,12 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
           <t>farm-e56757363b191415</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
@@ -8475,12 +8475,12 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
           <t>farm-e56757363b191415</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
@@ -8511,12 +8511,12 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
           <t>farm-e56757363b191415</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
@@ -8547,12 +8547,12 @@
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
           <t>farm-7f29a9b7e4429b3f</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C62" s="16" t="n">
@@ -8583,12 +8583,12 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
           <t>farm-eed961522354b1db</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
@@ -8619,12 +8619,12 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
           <t>farm-eed961522354b1db</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
@@ -8655,12 +8655,12 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
           <t>farm-eed961522354b1db</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
@@ -8691,12 +8691,12 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
           <t>farm-eed961522354b1db</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
@@ -8727,12 +8727,12 @@
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
           <t>farm-eed961522354b1db</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
@@ -8763,12 +8763,12 @@
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
           <t>farm-305accaece5919b4</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C68" s="16" t="n">
@@ -8799,12 +8799,12 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
@@ -8835,12 +8835,12 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
@@ -8871,12 +8871,12 @@
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
@@ -8907,12 +8907,12 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
@@ -8943,12 +8943,12 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
@@ -8979,12 +8979,12 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
@@ -9015,12 +9015,12 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
           <t>farm-b1e4cf9777609738</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
@@ -9051,12 +9051,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>farm-ac5c64319b646dd9</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
@@ -9087,12 +9087,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
           <t>farm-ac5c64319b646dd9</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
@@ -9123,12 +9123,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
           <t>farm-ac5c64319b646dd9</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C78" s="4" t="n">
@@ -9159,12 +9159,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
           <t>farm-ac5c64319b646dd9</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
@@ -9195,12 +9195,12 @@
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
           <t>farm-ac5c64319b646dd9</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C80" s="16" t="n">
@@ -9231,12 +9231,12 @@
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
           <t>farm-af5a261842357d7e</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
@@ -9267,12 +9267,12 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
           <t>farm-af5a261842357d7e</t>
-        </is>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
@@ -9303,12 +9303,12 @@
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
           <t>farm-af5a261842357d7e</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
@@ -9339,12 +9339,12 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>farm-af5a261842357d7e</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
@@ -9375,12 +9375,12 @@
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
           <t>farm-af5a261842357d7e</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
@@ -9411,12 +9411,12 @@
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
           <t>farm-037e909e1f5ae0ac</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C86" s="16" t="n">
@@ -9447,12 +9447,12 @@
     <row r="87">
       <c r="A87" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
           <t>farm-d4377432e11c0aae</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
@@ -9483,12 +9483,12 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
           <t>farm-d4377432e11c0aae</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
@@ -9519,12 +9519,12 @@
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
           <t>farm-d4377432e11c0aae</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
@@ -9555,12 +9555,12 @@
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
           <t>farm-d4377432e11c0aae</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C90" s="12" t="n">
@@ -9591,12 +9591,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
           <t>farm-bc1775332e31d3a0</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
@@ -9627,12 +9627,12 @@
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
           <t>farm-bc1775332e31d3a0</t>
-        </is>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C92" s="16" t="n">
@@ -9663,12 +9663,12 @@
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
           <t>farm-6027017933654175</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
@@ -9699,12 +9699,12 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
           <t>farm-6027017933654175</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
@@ -9735,12 +9735,12 @@
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
           <t>farm-6027017933654175</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
@@ -9771,12 +9771,12 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
           <t>farm-6027017933654175</t>
-        </is>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
@@ -9807,12 +9807,12 @@
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
+          <t>Nowra_labels3.shp</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
           <t>farm-6027017933654175</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Nowra_labels3.shp</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
@@ -9843,12 +9843,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
@@ -9879,12 +9879,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
@@ -9915,12 +9915,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
@@ -9951,12 +9951,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
@@ -9987,12 +9987,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
@@ -10023,12 +10023,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
@@ -10059,12 +10059,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
@@ -10095,12 +10095,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
@@ -10131,12 +10131,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C106" s="4" t="n">
@@ -10167,12 +10167,12 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
           <t>farm-5a01809d68394e2e</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C107" s="16" t="n">
@@ -10203,12 +10203,12 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
@@ -10239,12 +10239,12 @@
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
@@ -10275,12 +10275,12 @@
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C110" s="8" t="n">
@@ -10311,12 +10311,12 @@
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C111" s="8" t="n">
@@ -10347,12 +10347,12 @@
     <row r="112">
       <c r="A112" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C112" s="8" t="n">
@@ -10383,12 +10383,12 @@
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C113" s="8" t="n">
@@ -10419,12 +10419,12 @@
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C114" s="8" t="n">
@@ -10459,12 +10459,12 @@
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C115" s="8" t="n">
@@ -10495,12 +10495,12 @@
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C116" s="8" t="n">
@@ -10531,12 +10531,12 @@
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
           <t>farm-a0ba66ca19262dbe</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C117" s="12" t="n">
@@ -10567,12 +10567,12 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
@@ -10603,12 +10603,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
@@ -10639,12 +10639,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
@@ -10675,12 +10675,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
@@ -10711,12 +10711,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
@@ -10747,12 +10747,12 @@
     <row r="123">
       <c r="A123" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
           <t>farm-5f5db65987d2b2be</t>
-        </is>
-      </c>
-      <c r="B123" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C123" s="16" t="n">
@@ -10783,12 +10783,12 @@
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
           <t>farm-4fabfad6e9be445d</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C124" s="8" t="n">
@@ -10819,12 +10819,12 @@
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
           <t>farm-4fabfad6e9be445d</t>
-        </is>
-      </c>
-      <c r="B125" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C125" s="12" t="n">
@@ -10855,12 +10855,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
           <t>farm-6663f1572ff9407d</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
@@ -10891,12 +10891,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
           <t>farm-6663f1572ff9407d</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
@@ -10927,12 +10927,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
           <t>farm-6663f1572ff9407d</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
@@ -10963,12 +10963,12 @@
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
           <t>farm-6663f1572ff9407d</t>
-        </is>
-      </c>
-      <c r="B129" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C129" s="16" t="n">
@@ -10999,12 +10999,12 @@
     <row r="130">
       <c r="A130" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
           <t>farm-b1275447db90b1b0</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C130" s="12" t="n">
@@ -11035,12 +11035,12 @@
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
           <t>farm-16a4bd6e448afbf7</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C131" s="16" t="n">
@@ -11071,12 +11071,12 @@
     <row r="132">
       <c r="A132" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
           <t>farm-db7d890c72e8d289</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C132" s="12" t="n">
@@ -11107,12 +11107,12 @@
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
           <t>farm-244ec28e52f7d3b6</t>
-        </is>
-      </c>
-      <c r="B133" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C133" s="16" t="n">
@@ -11143,12 +11143,12 @@
     <row r="134">
       <c r="A134" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
           <t>farm-48b1a81463554162</t>
-        </is>
-      </c>
-      <c r="B134" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C134" s="12" t="n">
@@ -11179,12 +11179,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
           <t>farm-4e5cfd71f42aff27</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
@@ -11215,12 +11215,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
           <t>farm-4e5cfd71f42aff27</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C136" s="4" t="n">
@@ -11251,12 +11251,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
           <t>farm-4e5cfd71f42aff27</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
@@ -11287,12 +11287,12 @@
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
           <t>farm-4e5cfd71f42aff27</t>
-        </is>
-      </c>
-      <c r="B138" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C138" s="16" t="n">
@@ -11323,12 +11323,12 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
           <t>farm-76571ee6ee6ffd61</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C139" s="12" t="n">
@@ -11359,12 +11359,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
           <t>farm-98dc08a8f634b5d1</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C140" s="4" t="n">
@@ -11395,12 +11395,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
           <t>farm-98dc08a8f634b5d1</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C141" s="4" t="n">
@@ -11431,12 +11431,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
           <t>farm-98dc08a8f634b5d1</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
@@ -11467,12 +11467,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
           <t>farm-98dc08a8f634b5d1</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C143" s="4" t="n">
@@ -11503,12 +11503,12 @@
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
           <t>farm-98dc08a8f634b5d1</t>
-        </is>
-      </c>
-      <c r="B144" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C144" s="16" t="n">
@@ -11539,12 +11539,12 @@
     <row r="145">
       <c r="A145" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
           <t>farm-403ed60a7fd41ebf</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C145" s="8" t="n">
@@ -11575,12 +11575,12 @@
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
           <t>farm-403ed60a7fd41ebf</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C146" s="8" t="n">
@@ -11611,12 +11611,12 @@
     <row r="147">
       <c r="A147" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
           <t>farm-403ed60a7fd41ebf</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C147" s="8" t="n">
@@ -11647,12 +11647,12 @@
     <row r="148">
       <c r="A148" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
           <t>farm-403ed60a7fd41ebf</t>
-        </is>
-      </c>
-      <c r="B148" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C148" s="8" t="n">
@@ -11683,12 +11683,12 @@
     <row r="149">
       <c r="A149" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
           <t>farm-403ed60a7fd41ebf</t>
-        </is>
-      </c>
-      <c r="B149" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C149" s="12" t="n">
@@ -11719,12 +11719,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
           <t>farm-77ffc5161ce89cd6</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C150" s="4" t="n">
@@ -11755,12 +11755,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
           <t>farm-77ffc5161ce89cd6</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C151" s="4" t="n">
@@ -11791,12 +11791,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
           <t>farm-77ffc5161ce89cd6</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C152" s="4" t="n">
@@ -11827,12 +11827,12 @@
     <row r="153">
       <c r="A153" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
           <t>farm-77ffc5161ce89cd6</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C153" s="16" t="n">
@@ -11863,12 +11863,12 @@
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
           <t>farm-9d61e7916f947b83</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C154" s="8" t="n">
@@ -11899,12 +11899,12 @@
     <row r="155">
       <c r="A155" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
           <t>farm-9d61e7916f947b83</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C155" s="12" t="n">
@@ -11935,12 +11935,12 @@
     <row r="156">
       <c r="A156" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
           <t>farm-378faa814fbaed38</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C156" s="16" t="n">
@@ -11971,12 +11971,12 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
           <t>farm-f31a7e9254df2121</t>
-        </is>
-      </c>
-      <c r="B157" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C157" s="8" t="n">
@@ -12007,12 +12007,12 @@
     <row r="158">
       <c r="A158" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
           <t>farm-f31a7e9254df2121</t>
-        </is>
-      </c>
-      <c r="B158" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C158" s="12" t="n">
@@ -12043,12 +12043,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
           <t>farm-0917e33745fd6d25</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C159" s="4" t="n">
@@ -12079,12 +12079,12 @@
     <row r="160">
       <c r="A160" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
           <t>farm-0917e33745fd6d25</t>
-        </is>
-      </c>
-      <c r="B160" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C160" s="16" t="n">
@@ -12115,12 +12115,12 @@
     <row r="161">
       <c r="A161" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
           <t>farm-42126df81f405428</t>
-        </is>
-      </c>
-      <c r="B161" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C161" s="12" t="n">
@@ -12151,12 +12151,12 @@
     <row r="162">
       <c r="A162" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
           <t>farm-e1edc0ed277da384</t>
-        </is>
-      </c>
-      <c r="B162" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C162" s="16" t="n">
@@ -12187,12 +12187,12 @@
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B163" s="12" t="inlineStr">
+        <is>
           <t>farm-6aee8825c7e649be</t>
-        </is>
-      </c>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C163" s="12" t="n">
@@ -12223,12 +12223,12 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C164" s="4" t="n">
@@ -12259,12 +12259,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
@@ -12299,12 +12299,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C166" s="4" t="n">
@@ -12335,12 +12335,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C167" s="4" t="n">
@@ -12375,12 +12375,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C168" s="4" t="n">
@@ -12411,12 +12411,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C169" s="4" t="n">
@@ -12451,12 +12451,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C170" s="4" t="n">
@@ -12487,12 +12487,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
@@ -12523,12 +12523,12 @@
     <row r="172">
       <c r="A172" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
           <t>farm-a6918664153f432e</t>
-        </is>
-      </c>
-      <c r="B172" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C172" s="16" t="n">
@@ -12559,12 +12559,12 @@
     <row r="173">
       <c r="A173" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B173" s="12" t="inlineStr">
+        <is>
           <t>farm-b94a7f5d05ced20a</t>
-        </is>
-      </c>
-      <c r="B173" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C173" s="12" t="n">
@@ -12595,12 +12595,12 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
           <t>farm-0eab511b21302fc0</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
@@ -12631,12 +12631,12 @@
     <row r="175">
       <c r="A175" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
           <t>farm-0eab511b21302fc0</t>
-        </is>
-      </c>
-      <c r="B175" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C175" s="16" t="n">
@@ -12667,12 +12667,12 @@
     <row r="176">
       <c r="A176" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B176" s="12" t="inlineStr">
+        <is>
           <t>farm-5edef7fd5cc44bcc</t>
-        </is>
-      </c>
-      <c r="B176" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C176" s="12" t="n">
@@ -12703,12 +12703,12 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
           <t>farm-e04cb65e43342bea</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
@@ -12739,12 +12739,12 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
           <t>farm-e04cb65e43342bea</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C178" s="4" t="n">
@@ -12775,12 +12775,12 @@
     <row r="179">
       <c r="A179" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
+        <is>
           <t>farm-e04cb65e43342bea</t>
-        </is>
-      </c>
-      <c r="B179" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C179" s="16" t="n">
@@ -12811,12 +12811,12 @@
     <row r="180">
       <c r="A180" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C180" s="8" t="n">
@@ -12847,12 +12847,12 @@
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
@@ -12883,12 +12883,12 @@
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C182" s="8" t="n">
@@ -12919,12 +12919,12 @@
     <row r="183">
       <c r="A183" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B183" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
@@ -12955,12 +12955,12 @@
     <row r="184">
       <c r="A184" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B184" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C184" s="8" t="n">
@@ -12991,12 +12991,12 @@
     <row r="185">
       <c r="A185" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
@@ -13027,12 +13027,12 @@
     <row r="186">
       <c r="A186" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B186" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C186" s="8" t="n">
@@ -13063,12 +13063,12 @@
     <row r="187">
       <c r="A187" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B187" s="12" t="inlineStr">
+        <is>
           <t>farm-c22b15ff4d5e0e6b</t>
-        </is>
-      </c>
-      <c r="B187" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C187" s="12" t="n">
@@ -13099,12 +13099,12 @@
     <row r="188">
       <c r="A188" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B188" s="16" t="inlineStr">
+        <is>
           <t>farm-46c1097774477779</t>
-        </is>
-      </c>
-      <c r="B188" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C188" s="16" t="n">
@@ -13135,12 +13135,12 @@
     <row r="189">
       <c r="A189" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
           <t>farm-ca77d119c32310fd</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
@@ -13171,12 +13171,12 @@
     <row r="190">
       <c r="A190" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B190" s="12" t="inlineStr">
+        <is>
           <t>farm-ca77d119c32310fd</t>
-        </is>
-      </c>
-      <c r="B190" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C190" s="12" t="n">
@@ -13207,12 +13207,12 @@
     <row r="191">
       <c r="A191" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B191" s="16" t="inlineStr">
+        <is>
           <t>farm-de50bdf28a62bc88</t>
-        </is>
-      </c>
-      <c r="B191" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C191" s="16" t="n">
@@ -13243,12 +13243,12 @@
     <row r="192">
       <c r="A192" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
           <t>farm-50a7d5199634a0da</t>
-        </is>
-      </c>
-      <c r="B192" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C192" s="8" t="n">
@@ -13279,12 +13279,12 @@
     <row r="193">
       <c r="A193" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
           <t>farm-50a7d5199634a0da</t>
-        </is>
-      </c>
-      <c r="B193" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C193" s="8" t="n">
@@ -13315,12 +13315,12 @@
     <row r="194">
       <c r="A194" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
           <t>farm-50a7d5199634a0da</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C194" s="8" t="n">
@@ -13351,12 +13351,12 @@
     <row r="195">
       <c r="A195" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
           <t>farm-50a7d5199634a0da</t>
-        </is>
-      </c>
-      <c r="B195" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C195" s="12" t="n">
@@ -13387,12 +13387,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
           <t>farm-3b73264647357ca2</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C196" s="4" t="n">
@@ -13423,12 +13423,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
           <t>farm-3b73264647357ca2</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C197" s="4" t="n">
@@ -13459,12 +13459,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
           <t>farm-3b73264647357ca2</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C198" s="4" t="n">
@@ -13495,12 +13495,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
           <t>farm-3b73264647357ca2</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C199" s="4" t="n">
@@ -13531,12 +13531,12 @@
     <row r="200">
       <c r="A200" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B200" s="16" t="inlineStr">
+        <is>
           <t>farm-3b73264647357ca2</t>
-        </is>
-      </c>
-      <c r="B200" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C200" s="16" t="n">
@@ -13567,12 +13567,12 @@
     <row r="201">
       <c r="A201" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
           <t>farm-be47380be0097c75</t>
-        </is>
-      </c>
-      <c r="B201" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C201" s="8" t="n">
@@ -13603,12 +13603,12 @@
     <row r="202">
       <c r="A202" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B202" s="12" t="inlineStr">
+        <is>
           <t>farm-be47380be0097c75</t>
-        </is>
-      </c>
-      <c r="B202" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C202" s="12" t="n">
@@ -13639,12 +13639,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
           <t>farm-f34e8576ace1680e</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C203" s="4" t="n">
@@ -13675,12 +13675,12 @@
     <row r="204">
       <c r="A204" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B204" s="16" t="inlineStr">
+        <is>
           <t>farm-f34e8576ace1680e</t>
-        </is>
-      </c>
-      <c r="B204" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C204" s="16" t="n">
@@ -13711,12 +13711,12 @@
     <row r="205">
       <c r="A205" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B205" s="12" t="inlineStr">
+        <is>
           <t>farm-f646aac5897fa0a0</t>
-        </is>
-      </c>
-      <c r="B205" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C205" s="12" t="n">
@@ -13747,12 +13747,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
           <t>farm-89a91fedcf7b3e2d</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C206" s="4" t="n">
@@ -13783,12 +13783,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
           <t>farm-89a91fedcf7b3e2d</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C207" s="4" t="n">
@@ -13819,12 +13819,12 @@
     <row r="208">
       <c r="A208" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B208" s="16" t="inlineStr">
+        <is>
           <t>farm-89a91fedcf7b3e2d</t>
-        </is>
-      </c>
-      <c r="B208" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C208" s="16" t="n">
@@ -13855,12 +13855,12 @@
     <row r="209">
       <c r="A209" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B209" s="12" t="inlineStr">
+        <is>
           <t>farm-c8b49065835d2604</t>
-        </is>
-      </c>
-      <c r="B209" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C209" s="12" t="n">
@@ -13891,12 +13891,12 @@
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B210" s="16" t="inlineStr">
+        <is>
           <t>farm-fbf74ce631c7a094</t>
-        </is>
-      </c>
-      <c r="B210" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C210" s="16" t="n">
@@ -13927,12 +13927,12 @@
     <row r="211">
       <c r="A211" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B211" s="12" t="inlineStr">
+        <is>
           <t>farm-e206fc0bc6df3cad</t>
-        </is>
-      </c>
-      <c r="B211" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C211" s="12" t="n">
@@ -13963,12 +13963,12 @@
     <row r="212">
       <c r="A212" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B212" s="16" t="inlineStr">
+        <is>
           <t>farm-9ca14a5bc58e10f9</t>
-        </is>
-      </c>
-      <c r="B212" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C212" s="16" t="n">
@@ -13999,12 +13999,12 @@
     <row r="213">
       <c r="A213" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B213" s="12" t="inlineStr">
+        <is>
           <t>farm-d28006827dd1894b</t>
-        </is>
-      </c>
-      <c r="B213" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C213" s="12" t="n">
@@ -14035,12 +14035,12 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
           <t>farm-b352036320a4167f</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C214" s="4" t="n">
@@ -14071,12 +14071,12 @@
     <row r="215">
       <c r="A215" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B215" s="16" t="inlineStr">
+        <is>
           <t>farm-b352036320a4167f</t>
-        </is>
-      </c>
-      <c r="B215" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C215" s="16" t="n">
@@ -14107,12 +14107,12 @@
     <row r="216">
       <c r="A216" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B216" s="12" t="inlineStr">
+        <is>
           <t>farm-818947903f93d1f6</t>
-        </is>
-      </c>
-      <c r="B216" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C216" s="12" t="n">
@@ -14143,12 +14143,12 @@
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B217" s="16" t="inlineStr">
+        <is>
           <t>farm-0a81d2f16e4f8496</t>
-        </is>
-      </c>
-      <c r="B217" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C217" s="16" t="n">
@@ -14179,12 +14179,12 @@
     <row r="218">
       <c r="A218" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B218" s="8" t="inlineStr">
+        <is>
           <t>farm-393753335beb054e</t>
-        </is>
-      </c>
-      <c r="B218" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C218" s="8" t="n">
@@ -14215,12 +14215,12 @@
     <row r="219">
       <c r="A219" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
           <t>farm-393753335beb054e</t>
-        </is>
-      </c>
-      <c r="B219" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
@@ -14251,12 +14251,12 @@
     <row r="220">
       <c r="A220" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="inlineStr">
+        <is>
           <t>farm-393753335beb054e</t>
-        </is>
-      </c>
-      <c r="B220" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C220" s="8" t="n">
@@ -14287,12 +14287,12 @@
     <row r="221">
       <c r="A221" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
           <t>farm-393753335beb054e</t>
-        </is>
-      </c>
-      <c r="B221" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
@@ -14323,12 +14323,12 @@
     <row r="222">
       <c r="A222" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B222" s="12" t="inlineStr">
+        <is>
           <t>farm-393753335beb054e</t>
-        </is>
-      </c>
-      <c r="B222" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C222" s="12" t="n">
@@ -14359,12 +14359,12 @@
     <row r="223">
       <c r="A223" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B223" s="16" t="inlineStr">
+        <is>
           <t>farm-b2341f5ff3f48af2</t>
-        </is>
-      </c>
-      <c r="B223" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C223" s="16" t="n">
@@ -14395,12 +14395,12 @@
     <row r="224">
       <c r="A224" s="8" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
           <t>farm-c5b8bbd58c7a19c7</t>
-        </is>
-      </c>
-      <c r="B224" s="8" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C224" s="8" t="n">
@@ -14431,12 +14431,12 @@
     <row r="225">
       <c r="A225" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B225" s="12" t="inlineStr">
+        <is>
           <t>farm-c5b8bbd58c7a19c7</t>
-        </is>
-      </c>
-      <c r="B225" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C225" s="12" t="n">
@@ -14467,12 +14467,12 @@
     <row r="226">
       <c r="A226" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B226" s="16" t="inlineStr">
+        <is>
           <t>farm-9b31a7c4658ffbc4</t>
-        </is>
-      </c>
-      <c r="B226" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C226" s="16" t="n">
@@ -14503,12 +14503,12 @@
     <row r="227">
       <c r="A227" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B227" s="12" t="inlineStr">
+        <is>
           <t>farm-b408aa99dd6b49c3</t>
-        </is>
-      </c>
-      <c r="B227" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C227" s="12" t="n">
@@ -14539,12 +14539,12 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
           <t>farm-0d9cf959fea36fb6</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C228" s="4" t="n">
@@ -14575,12 +14575,12 @@
     <row r="229">
       <c r="A229" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B229" s="16" t="inlineStr">
+        <is>
           <t>farm-0d9cf959fea36fb6</t>
-        </is>
-      </c>
-      <c r="B229" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C229" s="16" t="n">
@@ -14611,12 +14611,12 @@
     <row r="230">
       <c r="A230" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B230" s="12" t="inlineStr">
+        <is>
           <t>farm-dbffb518572c2a8e</t>
-        </is>
-      </c>
-      <c r="B230" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C230" s="12" t="n">
@@ -14647,12 +14647,12 @@
     <row r="231">
       <c r="A231" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B231" s="16" t="inlineStr">
+        <is>
           <t>farm-8b490b53d3476ae3</t>
-        </is>
-      </c>
-      <c r="B231" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C231" s="16" t="n">
@@ -14683,12 +14683,12 @@
     <row r="232">
       <c r="A232" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B232" s="12" t="inlineStr">
+        <is>
           <t>farm-79ebf6bb7857b01d</t>
-        </is>
-      </c>
-      <c r="B232" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C232" s="12" t="n">
@@ -14719,12 +14719,12 @@
     <row r="233">
       <c r="A233" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B233" s="16" t="inlineStr">
+        <is>
           <t>farm-c4f666615a54cd69</t>
-        </is>
-      </c>
-      <c r="B233" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C233" s="16" t="n">
@@ -14755,12 +14755,12 @@
     <row r="234">
       <c r="A234" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr">
+        <is>
           <t>farm-2023e6494cc05395</t>
-        </is>
-      </c>
-      <c r="B234" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C234" s="12" t="n">
@@ -14791,12 +14791,12 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
           <t>farm-2296fd66f82b7c0c</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C235" s="4" t="n">
@@ -14827,12 +14827,12 @@
     <row r="236">
       <c r="A236" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B236" s="16" t="inlineStr">
+        <is>
           <t>farm-2296fd66f82b7c0c</t>
-        </is>
-      </c>
-      <c r="B236" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C236" s="16" t="n">
@@ -14863,12 +14863,12 @@
     <row r="237">
       <c r="A237" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B237" s="12" t="inlineStr">
+        <is>
           <t>farm-e74a59dfdf2ba825</t>
-        </is>
-      </c>
-      <c r="B237" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C237" s="12" t="n">
@@ -14899,12 +14899,12 @@
     <row r="238">
       <c r="A238" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B238" s="16" t="inlineStr">
+        <is>
           <t>farm-ef359e9395f5316b</t>
-        </is>
-      </c>
-      <c r="B238" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C238" s="16" t="n">
@@ -14935,12 +14935,12 @@
     <row r="239">
       <c r="A239" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B239" s="12" t="inlineStr">
+        <is>
           <t>farm-cccfb0ef4c418994</t>
-        </is>
-      </c>
-      <c r="B239" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C239" s="12" t="n">
@@ -14971,12 +14971,12 @@
     <row r="240">
       <c r="A240" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B240" s="16" t="inlineStr">
+        <is>
           <t>farm-c2e233ed7bdd157a</t>
-        </is>
-      </c>
-      <c r="B240" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C240" s="16" t="n">
@@ -15007,12 +15007,12 @@
     <row r="241">
       <c r="A241" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B241" s="12" t="inlineStr">
+        <is>
           <t>farm-78156461891034d4</t>
-        </is>
-      </c>
-      <c r="B241" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C241" s="12" t="n">
@@ -15043,12 +15043,12 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
           <t>farm-7a779bf2435f46d6</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C242" s="4" t="n">
@@ -15079,12 +15079,12 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
           <t>farm-7a779bf2435f46d6</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C243" s="4" t="n">
@@ -15115,12 +15115,12 @@
     <row r="244">
       <c r="A244" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B244" s="16" t="inlineStr">
+        <is>
           <t>farm-7a779bf2435f46d6</t>
-        </is>
-      </c>
-      <c r="B244" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C244" s="16" t="n">
@@ -15151,12 +15151,12 @@
     <row r="245">
       <c r="A245" s="12" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B245" s="12" t="inlineStr">
+        <is>
           <t>farm-e449759ff2c26029</t>
-        </is>
-      </c>
-      <c r="B245" s="12" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C245" s="12" t="n">
@@ -15187,12 +15187,12 @@
     <row r="246">
       <c r="A246" s="16" t="inlineStr">
         <is>
+          <t>Bega_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B246" s="16" t="inlineStr">
+        <is>
           <t>farm-87ce4b159638edc3</t>
-        </is>
-      </c>
-      <c r="B246" s="16" t="inlineStr">
-        <is>
-          <t>Bega_labels2.shp</t>
         </is>
       </c>
       <c r="C246" s="16" t="n">
@@ -15223,12 +15223,12 @@
     <row r="247">
       <c r="A247" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B247" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C247" s="8" t="n">
@@ -15259,12 +15259,12 @@
     <row r="248">
       <c r="A248" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B248" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C248" s="8" t="n">
@@ -15295,12 +15295,12 @@
     <row r="249">
       <c r="A249" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B249" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C249" s="8" t="n">
@@ -15331,12 +15331,12 @@
     <row r="250">
       <c r="A250" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C250" s="8" t="n">
@@ -15367,12 +15367,12 @@
     <row r="251">
       <c r="A251" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B251" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C251" s="8" t="n">
@@ -15403,12 +15403,12 @@
     <row r="252">
       <c r="A252" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B252" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C252" s="8" t="n">
@@ -15439,12 +15439,12 @@
     <row r="253">
       <c r="A253" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B253" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
@@ -15475,12 +15475,12 @@
     <row r="254">
       <c r="A254" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B254" s="12" t="inlineStr">
+        <is>
           <t>farm-d882cfda97bcb875</t>
-        </is>
-      </c>
-      <c r="B254" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C254" s="12" t="n">
@@ -15511,12 +15511,12 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C255" s="4" t="n">
@@ -15547,12 +15547,12 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C256" s="4" t="n">
@@ -15583,12 +15583,12 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C257" s="4" t="n">
@@ -15619,12 +15619,12 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C258" s="4" t="n">
@@ -15659,12 +15659,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C259" s="4" t="n">
@@ -15695,12 +15695,12 @@
     <row r="260">
       <c r="A260" s="16" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B260" s="16" t="inlineStr">
+        <is>
           <t>farm-e816bcabcad7b8b8</t>
-        </is>
-      </c>
-      <c r="B260" s="16" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C260" s="16" t="n">
@@ -15731,12 +15731,12 @@
     <row r="261">
       <c r="A261" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B261" s="8" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B261" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
@@ -15767,12 +15767,12 @@
     <row r="262">
       <c r="A262" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B262" s="8" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B262" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C262" s="8" t="n">
@@ -15803,12 +15803,12 @@
     <row r="263">
       <c r="A263" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B263" s="8" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B263" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
@@ -15839,12 +15839,12 @@
     <row r="264">
       <c r="A264" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B264" s="8" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B264" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C264" s="8" t="n">
@@ -15879,12 +15879,12 @@
     <row r="265">
       <c r="A265" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B265" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C265" s="8" t="n">
@@ -15915,12 +15915,12 @@
     <row r="266">
       <c r="A266" s="8" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B266" s="8" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B266" s="8" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C266" s="8" t="n">
@@ -15951,12 +15951,12 @@
     <row r="267">
       <c r="A267" s="12" t="inlineStr">
         <is>
+          <t>Freemans_labels2.shp</t>
+        </is>
+      </c>
+      <c r="B267" s="12" t="inlineStr">
+        <is>
           <t>farm-aaa87e4ff1710d8c</t>
-        </is>
-      </c>
-      <c r="B267" s="12" t="inlineStr">
-        <is>
-          <t>Freemans_labels2.shp</t>
         </is>
       </c>
       <c r="C267" s="12" t="n">
